--- a/target/test-classes/TestData/OCW_TestCases.xlsx
+++ b/target/test-classes/TestData/OCW_TestCases.xlsx
@@ -1,31 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\varti\eclipse-workspace\CucumberJava\src\test\resources\TestData\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E797BF-C41D-41F7-8ADB-626033234254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="2810" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="19200" windowHeight="6800"/>
   </bookViews>
   <sheets>
     <sheet name="OCWTestData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
   <si>
     <t>Scenario</t>
   </si>
@@ -42,6 +44,42 @@
     <t>Password</t>
   </si>
   <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>MeterStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Previous Meter Reading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+current Meter Reading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+system Reading</t>
+  </si>
+  <si>
+    <t>current Water Charges</t>
+  </si>
+  <si>
+    <t>raw Water Surcharge</t>
+  </si>
+  <si>
+    <t>electricity Surcharge</t>
+  </si>
+  <si>
+    <t>meterRent</t>
+  </si>
+  <si>
+    <t>otherCharges</t>
+  </si>
+  <si>
+    <t>uploadImage</t>
+  </si>
+  <si>
     <t>User should be able to login with valid credentials</t>
   </si>
   <si>
@@ -51,52 +89,387 @@
     <t>TC_01LoginFuctionality</t>
   </si>
   <si>
+    <t>atul.gondane@veolia.com</t>
+  </si>
+  <si>
     <t>Test@123</t>
   </si>
   <si>
-    <t>anand.dhepe@veolia.com</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Verify</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>is</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>able</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>navigate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>to</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>bill</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Generation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>page</t>
+    </r>
+  </si>
+  <si>
+    <t>TC02</t>
+  </si>
+  <si>
+    <t>TC_02BillGeneration_001</t>
+  </si>
+  <si>
+    <t>53001432</t>
+  </si>
+  <si>
+    <t>Meter Ok</t>
+  </si>
+  <si>
+    <t>450</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>C:\Users\varti\Pictures\Screenshots\Screenshot 2025-05-14 114823 - Copy.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Consolas"/>
-      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0080FF"/>
       <name val="Consolas"/>
-      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -105,18 +478,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -126,26 +673,266 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -156,20 +943,71 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -218,7 +1056,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -253,7 +1091,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -427,66 +1265,160 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:P3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="26.1796875" customWidth="1"/>
-    <col min="2" max="2" width="21.453125" customWidth="1"/>
-    <col min="3" max="3" width="25.81640625" customWidth="1"/>
-    <col min="4" max="4" width="27.81640625" customWidth="1"/>
-    <col min="5" max="5" width="18.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.6363636363636" customWidth="1"/>
+    <col min="2" max="2" width="13.0909090909091" customWidth="1"/>
+    <col min="3" max="3" width="25.8181818181818" customWidth="1"/>
+    <col min="4" max="4" width="24.2727272727273" customWidth="1"/>
+    <col min="5" max="5" width="18.4545454545455" customWidth="1"/>
+    <col min="7" max="7" width="16.0909090909091" customWidth="1"/>
+    <col min="8" max="8" width="28.3636363636364" customWidth="1"/>
+    <col min="9" max="9" width="24.1818181818182" customWidth="1"/>
+    <col min="10" max="10" width="18.9090909090909" customWidth="1"/>
+    <col min="11" max="11" width="23.9090909090909" customWidth="1"/>
+    <col min="12" max="12" width="22.3636363636364" customWidth="1"/>
+    <col min="13" max="13" width="20.8181818181818" customWidth="1"/>
+    <col min="14" max="14" width="13.6363636363636" customWidth="1"/>
+    <col min="15" max="15" width="14.5454545454545" customWidth="1"/>
+    <col min="16" max="16" width="14.0909090909091" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="22" customHeight="1" spans="1:16">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" ht="39.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
+    <row r="2" ht="39" spans="1:16">
+      <c r="A2" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>8</v>
+        <v>17</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="P2" s="9"/>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="39" spans="1:16">
+      <c r="A3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{548551CB-FCBF-4B34-8A93-A5C4C938C7AF}"/>
-    <hyperlink ref="E2" r:id="rId2" xr:uid="{FDD1E3DE-E91B-48F0-9281-C03854865A3C}"/>
+    <hyperlink ref="D2" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="E2" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="D3" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="E3" r:id="rId2" display="Test@123"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>